--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-organization-pharmacy-licence.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-organization-pharmacy-licence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>Numéro de la licence d'exploitation d’une officine.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroLicence</t>
+    <t>Synonyme : numeroLicence</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
